--- a/tool_info/TOOLS_SEARCH_DB.xlsx
+++ b/tool_info/TOOLS_SEARCH_DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28cec7277d07af5d/Documents/project_suggester/tool_info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3B65FA53-3425-41D5-9EBB-2893DD228A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70209F4D-FB50-44AC-8D91-0A83A08586BC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3B65FA53-3425-41D5-9EBB-2893DD228A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA206968-69C8-427F-9C6F-BFEF22CB268D}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -132,11 +132,6 @@
   </si>
   <si>
     <t>OPEN_LIBRARY</t>
-  </si>
-  <si>
-    <t>Convert the following request into an Open Library search query.
-Focus on books, authors, literature and reading materials.
-Return only the search query.</t>
   </si>
   <si>
     <t>books ; novels ; authors ; literature ; reading ; book recommendations ; ISBN ; classic books ; publications</t>
@@ -315,6 +310,42 @@
 QUERY: Shakespeare;Sonnet
 Do not explain.
 Return only the output.</t>
+  </si>
+  <si>
+    <t>Convert the following request into an Open Library search query.
+Focus on:
+- books
+- novels
+- textbooks
+- authors
+- literature
+- reading materials
+- educational resources
+- ISBNs
+- subjects
+Rules:
+- Include important keywords.
+- Include book titles if mentioned.
+- Include author names if mentioned.
+- Include subjects if mentioned.
+- Remove unnecessary words.
+- Keep the query concise.
+- Separate words with spaces.
+- Do not explain.
+Examples:
+User request:
+Books by Stephen King
+QUERY: Stephen King
+User request:
+Machine learning textbooks
+QUERY: machine learning
+User request:
+Deep learning by Ian Goodfellow
+QUERY: deep learning Ian Goodfellow
+User request:
+Books on operating systems and computer networks
+QUERY: operating systems computer networks
+Return ONLY the query.</t>
   </si>
 </sst>
 </file>
@@ -370,6 +401,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -738,7 +773,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -747,157 +782,157 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" t="s">
         <v>61</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
         <v>69</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" t="s">
         <v>71</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>72</v>
-      </c>
-      <c r="E15" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
